--- a/data/Service Unit KPIs.xlsx
+++ b/data/Service Unit KPIs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="14_{01688352-53F1-4760-B109-B5441C10BA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA4F7D39-95A0-4CFB-A6C9-9192F400A0B0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870AF959-00C9-481E-ACF8-2548E1BA130E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>Number of datasets submitted</t>
   </si>
@@ -145,14 +145,29 @@
   <si>
     <t>Youth</t>
   </si>
+  <si>
+    <t>2026 Actual value</t>
+  </si>
+  <si>
+    <t>2027 Actual value</t>
+  </si>
+  <si>
+    <t>2028 Actual value</t>
+  </si>
+  <si>
+    <t>2029 Actual value</t>
+  </si>
+  <si>
+    <t>2030 Actual value</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -604,9 +619,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -627,10 +642,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -660,19 +675,10 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -693,10 +699,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -705,16 +711,16 @@
     <xf numFmtId="9" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -726,13 +732,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -747,9 +747,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -759,25 +756,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -792,29 +777,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -828,14 +801,53 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1174,20 +1186,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD7994F9-868B-4600-9F9F-308CB16C1B42}">
   <dimension ref="A1:XFC32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.6328125" style="60" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" style="60" customWidth="1"/>
-    <col min="3" max="3" width="7.90625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" style="50" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" style="50" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16383" s="5" customFormat="1" ht="24.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:16383" s="5" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="36" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -1196,10 +1208,21 @@
       <c r="D1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="2"/>
+      <c r="E1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="J1" s="3"/>
       <c r="K1" s="4"/>
       <c r="L1" s="1"/>
@@ -17575,245 +17598,260 @@
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="4"/>
     </row>
-    <row r="2" spans="1:16383" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
+    <row r="2" spans="1:16383" x14ac:dyDescent="0.3">
+      <c r="A2" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="71">
         <v>0.8</v>
       </c>
       <c r="D2" s="10">
         <v>0.63</v>
       </c>
     </row>
-    <row r="3" spans="1:16383" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+    <row r="3" spans="1:16383" x14ac:dyDescent="0.3">
+      <c r="A3" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="20"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="72"/>
       <c r="D3" s="11">
         <v>0.74</v>
       </c>
     </row>
-    <row r="4" spans="1:16383" x14ac:dyDescent="0.35">
-      <c r="A4" s="42" t="s">
+    <row r="4" spans="1:16383" x14ac:dyDescent="0.3">
+      <c r="A4" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="20"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="72"/>
       <c r="D4" s="11">
         <v>0.81</v>
       </c>
     </row>
-    <row r="5" spans="1:16383" x14ac:dyDescent="0.35">
-      <c r="A5" s="42" t="s">
+    <row r="5" spans="1:16383" x14ac:dyDescent="0.3">
+      <c r="A5" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="72"/>
       <c r="D5" s="11">
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:16383" x14ac:dyDescent="0.35">
-      <c r="A6" s="42" t="s">
+    <row r="6" spans="1:16383" ht="24" x14ac:dyDescent="0.3">
+      <c r="A6" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="20"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="72"/>
       <c r="D6" s="11">
         <v>0.59</v>
       </c>
     </row>
-    <row r="7" spans="1:16383" x14ac:dyDescent="0.35">
-      <c r="A7" s="42" t="s">
+    <row r="7" spans="1:16383" x14ac:dyDescent="0.3">
+      <c r="A7" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="20"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="11">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:16383" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="44" t="s">
+    <row r="8" spans="1:16383" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="21"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="73"/>
       <c r="D8" s="12">
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:16383" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="62" t="s">
+    <row r="9" spans="1:16383" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="20" t="s">
         <v>21</v>
       </c>
+      <c r="E9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="10" spans="1:16383" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="70" t="s">
+    <row r="10" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="27">
         <v>150</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="28">
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:16383" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="68"/>
-      <c r="B11" s="72" t="s">
+    <row r="11" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="75"/>
+      <c r="B11" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="29">
         <v>0.5</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="30">
         <v>0.59</v>
       </c>
     </row>
-    <row r="12" spans="1:16383" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="68"/>
-      <c r="B12" s="42" t="s">
+    <row r="12" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75"/>
+      <c r="B12" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="31">
         <v>60</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="32">
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:16383" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="68"/>
-      <c r="B13" s="73" t="s">
+    <row r="13" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="75"/>
+      <c r="B13" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="29">
         <v>0.5</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="33">
         <v>0.49</v>
       </c>
     </row>
-    <row r="14" spans="1:16383" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="68"/>
-      <c r="B14" s="42" t="s">
+    <row r="14" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="75"/>
+      <c r="B14" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="34">
         <v>12000</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="32">
         <v>12612</v>
       </c>
     </row>
-    <row r="15" spans="1:16383" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="68"/>
-      <c r="B15" s="73" t="s">
+    <row r="15" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="75"/>
+      <c r="B15" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="29">
         <v>0.5</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="33">
         <v>0.44</v>
       </c>
     </row>
-    <row r="16" spans="1:16383" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="68"/>
-      <c r="B16" s="42" t="s">
+    <row r="16" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="75"/>
+      <c r="B16" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="34">
         <v>150</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="32">
         <v>1444</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="68"/>
-      <c r="B17" s="73" t="s">
+    <row r="17" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="75"/>
+      <c r="B17" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="64">
+      <c r="C17" s="54">
         <v>0.5</v>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="33">
         <v>0.34</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="68"/>
-      <c r="B18" s="74" t="s">
+    <row r="18" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="75"/>
+      <c r="B18" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="53">
         <v>30</v>
       </c>
-      <c r="D18" s="75">
+      <c r="D18" s="61">
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="68"/>
-      <c r="B19" s="74" t="s">
+    <row r="19" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="75"/>
+      <c r="B19" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="63">
+      <c r="C19" s="53">
         <v>30</v>
       </c>
-      <c r="D19" s="75">
+      <c r="D19" s="61">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="69"/>
-      <c r="B20" s="76" t="s">
+    <row r="20" spans="1:4" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="76"/>
+      <c r="B20" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="65">
+      <c r="C20" s="55">
         <v>30</v>
       </c>
-      <c r="D20" s="77">
+      <c r="D20" s="63">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="55" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="25">
         <v>50</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="26">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="58"/>
-      <c r="B22" s="59" t="s">
+    <row r="22" spans="1:4" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="67"/>
+      <c r="B22" s="49" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="13">
@@ -17823,33 +17861,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="50" t="s">
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="67"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="56"/>
     </row>
-    <row r="24" spans="1:4" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="51" t="s">
+    <row r="24" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="21">
         <v>0.5</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="22">
         <v>0.8</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="53" t="s">
+    <row r="25" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="47" t="s">
         <v>2</v>
       </c>
       <c r="C25" s="15">
@@ -17860,11 +17898,11 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="53" t="s">
+    <row r="26" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="47" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="15">
@@ -17874,11 +17912,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="24" x14ac:dyDescent="0.35">
-      <c r="A27" s="55" t="s">
+    <row r="27" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+      <c r="A27" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="48" t="s">
         <v>4</v>
       </c>
       <c r="C27" s="17">
@@ -17888,9 +17926,9 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="24" x14ac:dyDescent="0.35">
-      <c r="A28" s="57"/>
-      <c r="B28" s="46" t="s">
+    <row r="28" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+      <c r="A28" s="65"/>
+      <c r="B28" s="41" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="6">
@@ -17900,9 +17938,9 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="36" x14ac:dyDescent="0.35">
-      <c r="A29" s="57"/>
-      <c r="B29" s="46" t="s">
+    <row r="29" spans="1:4" ht="36" x14ac:dyDescent="0.3">
+      <c r="A29" s="65"/>
+      <c r="B29" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="6">
@@ -17912,9 +17950,9 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="24" x14ac:dyDescent="0.35">
-      <c r="A30" s="57"/>
-      <c r="B30" s="46" t="s">
+    <row r="30" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+      <c r="A30" s="65"/>
+      <c r="B30" s="41" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="6">
@@ -17924,25 +17962,25 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="48"/>
-      <c r="B31" s="49" t="s">
+    <row r="31" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="66"/>
+      <c r="B31" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="23">
         <v>1</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="24">
         <v>0.71</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="50" t="s">
+    <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="66"/>
-      <c r="C32" s="66"/>
-      <c r="D32" s="67"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -17955,4 +17993,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/Service Unit KPIs.xlsx
+++ b/data/Service Unit KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870AF959-00C9-481E-ACF8-2548E1BA130E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3959592A-E29F-4060-A714-A62C4DF07E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="42">
   <si>
     <t>Number of datasets submitted</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>2030 Actual value</t>
+  </si>
+  <si>
+    <t>KPI Metric</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1203,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>20</v>

--- a/data/Service Unit KPIs.xlsx
+++ b/data/Service Unit KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3959592A-E29F-4060-A714-A62C4DF07E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FBC3E5-94EE-4F96-A5B5-B589A46BAEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>Number of datasets submitted</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>KPI Metric</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -17868,7 +17871,9 @@
       <c r="A23" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="47"/>
+      <c r="B23" s="47" t="s">
+        <v>42</v>
+      </c>
       <c r="C23" s="47"/>
       <c r="D23" s="56"/>
     </row>
@@ -17981,7 +17986,9 @@
       <c r="A32" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="47"/>
+      <c r="B32" s="47" t="s">
+        <v>42</v>
+      </c>
       <c r="C32" s="47"/>
       <c r="D32" s="56"/>
     </row>

--- a/data/Service Unit KPIs.xlsx
+++ b/data/Service Unit KPIs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FBC3E5-94EE-4F96-A5B5-B589A46BAEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F338302-01E0-4462-8860-39DC80CBE6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
   </bookViews>
@@ -627,7 +627,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -664,9 +664,6 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1194,18 +1191,18 @@
   <dimension ref="A1:XFC32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" style="50" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" style="50" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" style="49" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" style="49" customWidth="1"/>
     <col min="3" max="3" width="7.88671875" style="7" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="7" customWidth="1"/>
     <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16383" s="5" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="35" t="s">
         <v>41</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -17605,13 +17602,13 @@
       <c r="XFC1" s="4"/>
     </row>
     <row r="2" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="71">
+      <c r="C2" s="70">
         <v>0.8</v>
       </c>
       <c r="D2" s="10">
@@ -17619,76 +17616,76 @@
       </c>
     </row>
     <row r="3" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="72"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="71"/>
       <c r="D3" s="11">
         <v>0.74</v>
       </c>
     </row>
     <row r="4" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="71"/>
       <c r="D4" s="11">
         <v>0.81</v>
       </c>
     </row>
     <row r="5" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="71"/>
       <c r="D5" s="11">
         <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="6" spans="1:16383" ht="24" x14ac:dyDescent="0.3">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="72"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="71"/>
       <c r="D6" s="11">
         <v>0.59</v>
       </c>
     </row>
     <row r="7" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="72"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="71"/>
       <c r="D7" s="11">
         <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="1:16383" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="73"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="72"/>
       <c r="D8" s="12">
         <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:16383" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>21</v>
       </c>
       <c r="E9" s="9" t="s">
@@ -17708,156 +17705,156 @@
       </c>
     </row>
     <row r="10" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>150</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="27">
         <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="75"/>
-      <c r="B11" s="58" t="s">
+      <c r="A11" s="74"/>
+      <c r="B11" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="28">
         <v>0.5</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>0.59</v>
       </c>
     </row>
     <row r="12" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="75"/>
-      <c r="B12" s="38" t="s">
+      <c r="A12" s="74"/>
+      <c r="B12" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <v>60</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="31">
         <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="75"/>
-      <c r="B13" s="59" t="s">
+      <c r="A13" s="74"/>
+      <c r="B13" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="28">
         <v>0.5</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="32">
         <v>0.49</v>
       </c>
     </row>
     <row r="14" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="75"/>
-      <c r="B14" s="38" t="s">
+      <c r="A14" s="74"/>
+      <c r="B14" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="33">
         <v>12000</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="31">
         <v>12612</v>
       </c>
     </row>
     <row r="15" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="75"/>
-      <c r="B15" s="59" t="s">
+      <c r="A15" s="74"/>
+      <c r="B15" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="28">
         <v>0.5</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="32">
         <v>0.44</v>
       </c>
     </row>
     <row r="16" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="75"/>
-      <c r="B16" s="38" t="s">
+      <c r="A16" s="74"/>
+      <c r="B16" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>150</v>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="31">
         <v>1444</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
-      <c r="B17" s="59" t="s">
+      <c r="A17" s="74"/>
+      <c r="B17" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="54">
+      <c r="C17" s="53">
         <v>0.5</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="32">
         <v>0.34</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
-      <c r="B18" s="60" t="s">
+      <c r="A18" s="74"/>
+      <c r="B18" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="53">
+      <c r="C18" s="52">
         <v>30</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D18" s="60">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="75"/>
-      <c r="B19" s="60" t="s">
+      <c r="A19" s="74"/>
+      <c r="B19" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="53">
+      <c r="C19" s="52">
         <v>30</v>
       </c>
-      <c r="D19" s="61">
+      <c r="D19" s="60">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="76"/>
-      <c r="B20" s="62" t="s">
+      <c r="A20" s="75"/>
+      <c r="B20" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="55">
+      <c r="C20" s="54">
         <v>30</v>
       </c>
-      <c r="D20" s="63">
+      <c r="D20" s="62">
         <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>50</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="25">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="67"/>
-      <c r="B22" s="49" t="s">
+      <c r="A22" s="66"/>
+      <c r="B22" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="13">
@@ -17868,75 +17865,74 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="47"/>
-      <c r="D23" s="56"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="55"/>
     </row>
     <row r="24" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="20">
         <v>0.5</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>0.8</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
         <v>20</v>
       </c>
-      <c r="D25" s="14">
-        <f>9/C25</f>
-        <v>0.45</v>
+      <c r="D25" s="15">
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <v>1</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A27" s="64" t="s">
+      <c r="A27" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="16">
         <v>1</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="17">
         <v>0.85</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A28" s="65"/>
-      <c r="B28" s="41" t="s">
+      <c r="A28" s="64"/>
+      <c r="B28" s="40" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="6">
@@ -17947,8 +17943,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="36" x14ac:dyDescent="0.3">
-      <c r="A29" s="65"/>
-      <c r="B29" s="41" t="s">
+      <c r="A29" s="64"/>
+      <c r="B29" s="40" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="6">
@@ -17959,8 +17955,8 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A30" s="65"/>
-      <c r="B30" s="41" t="s">
+      <c r="A30" s="64"/>
+      <c r="B30" s="40" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="6">
@@ -17971,26 +17967,26 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="66"/>
-      <c r="B31" s="43" t="s">
+      <c r="A31" s="65"/>
+      <c r="B31" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="23">
+      <c r="C31" s="22">
         <v>1</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="23">
         <v>0.71</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="44" t="s">
+      <c r="A32" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="56"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/data/Service Unit KPIs.xlsx
+++ b/data/Service Unit KPIs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F338302-01E0-4462-8860-39DC80CBE6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EB1459-2385-4DCA-96E1-7FB2F5C7028A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>Number of datasets submitted</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>Service Unit Key Performance Indicators (KPIs)</t>
-  </si>
-  <si>
-    <t>KP Metric</t>
   </si>
   <si>
     <t>Annual Target</t>
@@ -1191,7 +1188,7 @@
   <dimension ref="A1:XFC32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" style="49" customWidth="1"/>
+    <col min="1" max="1" width="37.88671875" style="49" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" style="49" customWidth="1"/>
     <col min="3" max="3" width="7.88671875" style="7" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="7" customWidth="1"/>
@@ -1203,28 +1200,28 @@
         <v>17</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>21</v>
+      <c r="E1" s="9" t="s">
+        <v>35</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="4"/>
@@ -17680,28 +17677,28 @@
         <v>18</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>21</v>
+      <c r="E9" s="9" t="s">
+        <v>35</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -17709,7 +17706,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="26">
         <v>150</v>
@@ -17721,7 +17718,7 @@
     <row r="11" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="74"/>
       <c r="B11" s="57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="28">
         <v>0.5</v>
@@ -17733,7 +17730,7 @@
     <row r="12" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="74"/>
       <c r="B12" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="30">
         <v>60</v>
@@ -17745,7 +17742,7 @@
     <row r="13" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="74"/>
       <c r="B13" s="58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="28">
         <v>0.5</v>
@@ -17757,7 +17754,7 @@
     <row r="14" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="74"/>
       <c r="B14" s="37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="33">
         <v>12000</v>
@@ -17769,7 +17766,7 @@
     <row r="15" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="74"/>
       <c r="B15" s="58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="28">
         <v>0.5</v>
@@ -17781,7 +17778,7 @@
     <row r="16" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="74"/>
       <c r="B16" s="37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="33">
         <v>150</v>
@@ -17793,7 +17790,7 @@
     <row r="17" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="74"/>
       <c r="B17" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="53">
         <v>0.5</v>
@@ -17805,7 +17802,7 @@
     <row r="18" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="74"/>
       <c r="B18" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="52">
         <v>30</v>
@@ -17817,7 +17814,7 @@
     <row r="19" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="74"/>
       <c r="B19" s="59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="52">
         <v>30</v>
@@ -17829,7 +17826,7 @@
     <row r="20" spans="1:4" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="75"/>
       <c r="B20" s="61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="54">
         <v>30</v>
@@ -17855,7 +17852,7 @@
     <row r="22" spans="1:4" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="66"/>
       <c r="B22" s="48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="13">
         <v>0.5</v>
@@ -17866,10 +17863,10 @@
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="55"/>
@@ -17980,10 +17977,10 @@
     </row>
     <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="46"/>
       <c r="D32" s="55"/>

--- a/data/Service Unit KPIs.xlsx
+++ b/data/Service Unit KPIs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EB1459-2385-4DCA-96E1-7FB2F5C7028A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE1D326-74B6-4CBD-804C-29B3A7884D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
   </bookViews>
@@ -122,13 +122,7 @@
     <t>Number of delivery partners trained</t>
   </si>
   <si>
-    <t>Number of delivery partners trained who are female</t>
-  </si>
-  <si>
     <t>Number of national scientists who attended training courses</t>
-  </si>
-  <si>
-    <t>Number of national scientists who attended training courses who are female</t>
   </si>
   <si>
     <t>Number of collaborations with Advanced Research Institutes (ARIs)</t>
@@ -162,6 +156,12 @@
   </si>
   <si>
     <t>In Progress</t>
+  </si>
+  <si>
+    <t>Percentage of national scientists who attended training courses who are female</t>
+  </si>
+  <si>
+    <t>Percentage of delivery partners trained who are female</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1200,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>19</v>
@@ -1209,19 +1209,19 @@
         <v>20</v>
       </c>
       <c r="E1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>39</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="4"/>
@@ -17677,7 +17677,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>19</v>
@@ -17686,19 +17686,19 @@
         <v>20</v>
       </c>
       <c r="E9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -17766,7 +17766,7 @@
     <row r="15" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="74"/>
       <c r="B15" s="58" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C15" s="28">
         <v>0.5</v>
@@ -17778,7 +17778,7 @@
     <row r="16" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="74"/>
       <c r="B16" s="37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="33">
         <v>150</v>
@@ -17790,7 +17790,7 @@
     <row r="17" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="74"/>
       <c r="B17" s="58" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C17" s="53">
         <v>0.5</v>
@@ -17802,7 +17802,7 @@
     <row r="18" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="74"/>
       <c r="B18" s="59" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C18" s="52">
         <v>30</v>
@@ -17814,7 +17814,7 @@
     <row r="19" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="74"/>
       <c r="B19" s="59" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C19" s="52">
         <v>30</v>
@@ -17826,7 +17826,7 @@
     <row r="20" spans="1:4" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="75"/>
       <c r="B20" s="61" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C20" s="54">
         <v>30</v>
@@ -17866,7 +17866,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="55"/>
@@ -17977,10 +17977,10 @@
     </row>
     <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" s="46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32" s="46"/>
       <c r="D32" s="55"/>

--- a/data/Service Unit KPIs.xlsx
+++ b/data/Service Unit KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE1D326-74B6-4CBD-804C-29B3A7884D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C62DFE-3AE6-4080-BE09-481D6290DB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
+    <workbookView xWindow="3768" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{B2484485-475C-4522-9B1B-61000E3901F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>Number of datasets submitted</t>
   </si>
@@ -98,9 +98,6 @@
     <t>Annual Target</t>
   </si>
   <si>
-    <t>2025 Actual value</t>
-  </si>
-  <si>
     <t>Percentage of datasets with a Findable, Accessible, Interopable, Reusable (FAIR) score above 3.</t>
   </si>
   <si>
@@ -137,21 +134,6 @@
     <t>Youth</t>
   </si>
   <si>
-    <t>2026 Actual value</t>
-  </si>
-  <si>
-    <t>2027 Actual value</t>
-  </si>
-  <si>
-    <t>2028 Actual value</t>
-  </si>
-  <si>
-    <t>2029 Actual value</t>
-  </si>
-  <si>
-    <t>2030 Actual value</t>
-  </si>
-  <si>
     <t>KPI Metric</t>
   </si>
   <si>
@@ -162,6 +144,24 @@
   </si>
   <si>
     <t>Percentage of delivery partners trained who are female</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>2030</t>
   </si>
 </sst>
 </file>
@@ -234,7 +234,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -473,17 +473,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -648,9 +637,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -678,25 +664,22 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -744,16 +727,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -774,7 +757,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -810,13 +793,16 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -840,14 +826,17 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1188,40 +1177,40 @@
   <dimension ref="A1:XFC32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.88671875" style="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" style="49" customWidth="1"/>
+    <col min="1" max="1" width="37.88671875" style="47" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" style="47" customWidth="1"/>
     <col min="3" max="3" width="7.88671875" style="7" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="7" customWidth="1"/>
     <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16383" s="5" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="35" t="s">
-        <v>38</v>
+      <c r="B1" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>20</v>
+      <c r="D1" s="61">
+        <v>2025</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>33</v>
+      <c r="E1" s="61">
+        <v>2026</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>34</v>
+      <c r="F1" s="61">
+        <v>2027</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>35</v>
+      <c r="G1" s="61">
+        <v>2028</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>36</v>
+      <c r="H1" s="61">
+        <v>2029</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>37</v>
+      <c r="I1" s="61">
+        <v>2030</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="4"/>
@@ -17599,391 +17588,391 @@
       <c r="XFC1" s="4"/>
     </row>
     <row r="2" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="70">
+      <c r="C2" s="69">
         <v>0.8</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>0.63</v>
       </c>
     </row>
     <row r="3" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="11">
+      <c r="B3" s="67"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="10">
         <v>0.74</v>
       </c>
     </row>
     <row r="4" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="11">
+      <c r="B4" s="67"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="10">
         <v>0.81</v>
       </c>
     </row>
     <row r="5" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="11">
+      <c r="B5" s="67"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="10">
         <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="6" spans="1:16383" ht="24" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="11">
+      <c r="B6" s="67"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="10">
         <v>0.59</v>
       </c>
     </row>
     <row r="7" spans="1:16383" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="11">
+      <c r="B7" s="67"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="10">
         <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="1:16383" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="12">
+      <c r="B8" s="68"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="11">
         <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:16383" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>19</v>
+      <c r="G9" s="75" t="s">
+        <v>39</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>20</v>
+      <c r="H9" s="75" t="s">
+        <v>40</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>37</v>
+      <c r="I9" s="75" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="56" t="s">
-        <v>23</v>
+      <c r="B10" s="54" t="s">
+        <v>22</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="24">
         <v>150</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="25">
         <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="74"/>
-      <c r="B11" s="57" t="s">
-        <v>24</v>
+      <c r="A11" s="73"/>
+      <c r="B11" s="55" t="s">
+        <v>23</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="26">
         <v>0.5</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="27">
         <v>0.59</v>
       </c>
     </row>
     <row r="12" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="74"/>
-      <c r="B12" s="37" t="s">
-        <v>25</v>
+      <c r="A12" s="73"/>
+      <c r="B12" s="35" t="s">
+        <v>24</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="28">
         <v>60</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="29">
         <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="74"/>
-      <c r="B13" s="58" t="s">
-        <v>26</v>
+      <c r="A13" s="73"/>
+      <c r="B13" s="56" t="s">
+        <v>25</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="26">
         <v>0.5</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="30">
         <v>0.49</v>
       </c>
     </row>
     <row r="14" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="74"/>
-      <c r="B14" s="37" t="s">
-        <v>27</v>
+      <c r="A14" s="73"/>
+      <c r="B14" s="35" t="s">
+        <v>26</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="31">
         <v>12000</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="29">
         <v>12612</v>
       </c>
     </row>
     <row r="15" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="74"/>
-      <c r="B15" s="58" t="s">
-        <v>41</v>
+      <c r="A15" s="73"/>
+      <c r="B15" s="56" t="s">
+        <v>35</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="26">
         <v>0.5</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="30">
         <v>0.44</v>
       </c>
     </row>
     <row r="16" spans="1:16383" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="74"/>
-      <c r="B16" s="37" t="s">
-        <v>28</v>
+      <c r="A16" s="73"/>
+      <c r="B16" s="35" t="s">
+        <v>27</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="31">
         <v>150</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="29">
         <v>1444</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="74"/>
-      <c r="B17" s="58" t="s">
-        <v>40</v>
+      <c r="A17" s="73"/>
+      <c r="B17" s="56" t="s">
+        <v>34</v>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="51">
         <v>0.5</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="30">
         <v>0.34</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="74"/>
-      <c r="B18" s="59" t="s">
-        <v>29</v>
+      <c r="A18" s="73"/>
+      <c r="B18" s="57" t="s">
+        <v>28</v>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="50">
         <v>30</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="58">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="74"/>
-      <c r="B19" s="59" t="s">
+      <c r="A19" s="73"/>
+      <c r="B19" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="50">
         <v>30</v>
       </c>
-      <c r="C19" s="52">
-        <v>30</v>
-      </c>
-      <c r="D19" s="60">
+      <c r="D19" s="58">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="75"/>
-      <c r="B20" s="61" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="54">
+      <c r="A20" s="74"/>
+      <c r="B20" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="62">
+      <c r="C20" s="52">
+        <v>30</v>
+      </c>
+      <c r="D20" s="60">
         <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="63" t="s">
+      <c r="A21" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="22">
         <v>50</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="23">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="66"/>
-      <c r="B22" s="48" t="s">
-        <v>21</v>
+      <c r="A22" s="65"/>
+      <c r="B22" s="46" t="s">
+        <v>20</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="12">
         <v>0.5</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="43" t="s">
-        <v>22</v>
+      <c r="A23" s="41" t="s">
+        <v>21</v>
       </c>
-      <c r="B23" s="46" t="s">
-        <v>39</v>
+      <c r="B23" s="44" t="s">
+        <v>33</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="55"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="53"/>
     </row>
     <row r="24" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="44" t="s">
+      <c r="A24" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="18">
         <v>0.5</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="19">
         <v>0.8</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13">
         <v>20</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="14">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="13">
         <v>1</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A27" s="63" t="s">
+      <c r="A27" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="16">
         <v>0.85</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A28" s="64"/>
-      <c r="B28" s="40" t="s">
+      <c r="A28" s="63"/>
+      <c r="B28" s="38" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="6">
         <v>0.6</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <v>0.38</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="36" x14ac:dyDescent="0.3">
-      <c r="A29" s="64"/>
-      <c r="B29" s="40" t="s">
+      <c r="A29" s="63"/>
+      <c r="B29" s="38" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="6">
         <v>1</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <v>0.36</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A30" s="64"/>
-      <c r="B30" s="40" t="s">
+      <c r="A30" s="63"/>
+      <c r="B30" s="38" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="6">
         <v>1</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <v>0.75</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="65"/>
-      <c r="B31" s="42" t="s">
+      <c r="A31" s="64"/>
+      <c r="B31" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="20">
         <v>1</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="21">
         <v>0.71</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="43" t="s">
-        <v>32</v>
+      <c r="A32" s="41" t="s">
+        <v>31</v>
       </c>
-      <c r="B32" s="46" t="s">
-        <v>39</v>
+      <c r="B32" s="44" t="s">
+        <v>33</v>
       </c>
-      <c r="C32" s="46"/>
-      <c r="D32" s="55"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="5">
